--- a/outputs/monitor_xlsx/20260409.xlsx
+++ b/outputs/monitor_xlsx/20260409.xlsx
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4772.6$</t>
+          <t>4792.2$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.90%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>98.52$</t>
+          <t>97.87$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+4.35%</t>
+          <t>+3.66%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>109.19%</t>
+          <t>141.14%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-18.14億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-362.81億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-18.14億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-362.81億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1159,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1254,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1342,12 +1336,7 @@
       <c r="N4" t="n">
         <v>-4628703</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1402,12 +1391,7 @@
       <c r="N5" t="n">
         <v>-78970</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1462,12 +1446,7 @@
       <c r="N6" t="n">
         <v>-649299</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1522,12 +1501,7 @@
       <c r="N7" t="n">
         <v>-6483090</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1582,12 +1556,7 @@
       <c r="N8" t="n">
         <v>-140275</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1642,12 +1611,7 @@
       <c r="N9" t="n">
         <v>-106299</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1702,12 +1666,7 @@
       <c r="N10" t="n">
         <v>-89546</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1716,12 +1675,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1730,44 +1689,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7995</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>2.37</v>
+        <v>2115</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-2.31</v>
       </c>
       <c r="F11" t="n">
-        <v>133</v>
+        <v>2783</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-12</v>
+        <v>-187</v>
       </c>
       <c r="H11" t="n">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>-199</v>
       </c>
       <c r="J11" t="n">
-        <v>-248</v>
+        <v>185</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="L11" t="n">
-        <v>317</v>
+        <v>3887</v>
       </c>
       <c r="M11" t="n">
-        <v>1305</v>
+        <v>15364</v>
       </c>
       <c r="N11" t="n">
-        <v>-8993</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19419</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1776,58 +1730,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2105</v>
+        <v>7995</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3.19</v>
+        <v>2.37</v>
       </c>
       <c r="F12" t="n">
-        <v>2931</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>226</v>
+        <v>133</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>-12</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="I12" t="n">
-        <v>-68</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>587</v>
+        <v>-248</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>317</v>
       </c>
       <c r="M12" t="n">
-        <v>213</v>
+        <v>1305</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8993</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1836,12 +1785,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1850,41 +1799,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>429</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.78</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>2073</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>23</v>
+        <v>226</v>
       </c>
       <c r="H13" t="n">
-        <v>93</v>
+        <v>18</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-68</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="K13" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L13" t="n">
-        <v>-151</v>
+        <v>17</v>
       </c>
       <c r="M13" t="n">
-        <v>-538</v>
+        <v>213</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1893,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1907,41 +1854,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>886</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-9.59</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>972</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>-383</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>485</v>
+        <v>93</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="L14" t="n">
-        <v>-64</v>
+        <v>-151</v>
       </c>
       <c r="M14" t="n">
-        <v>-270</v>
+        <v>-538</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1950,12 +1892,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1964,44 +1906,91 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1525</v>
+        <v>974</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>4.45</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>962</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-31</v>
+        <v>-383</v>
       </c>
       <c r="H15" t="n">
-        <v>-106</v>
-      </c>
-      <c r="I15" t="n">
-        <v>53</v>
+        <v>485</v>
       </c>
       <c r="J15" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>-64</v>
       </c>
       <c r="M15" t="n">
-        <v>91</v>
+        <v>-270</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="F16" t="n">
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-106</v>
+      </c>
+      <c r="I16" t="n">
+        <v>53</v>
+      </c>
+      <c r="J16" t="n">
+        <v>120</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>91</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/outputs/monitor_xlsx/20260409.xlsx
+++ b/outputs/monitor_xlsx/20260409.xlsx
@@ -544,10 +544,6 @@
           <t>+0.29%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.40%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-0.02%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+0.90%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>-0.55%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+2.10%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-7.37%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+3.66%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>317.8億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>288.41億</t>
@@ -807,7 +769,6 @@
           <t>13.57億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>57.99億</t>
@@ -818,8 +779,6 @@
           <t>289.97億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>131.04%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>393.33億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>7941口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>7815口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-14.72億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-32.69億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1994,6 +1937,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>576</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1465</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-82</v>
+      </c>
+      <c r="G17" t="n">
+        <v>829</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2462</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9842</v>
+      </c>
+      <c r="L17" t="n">
+        <v>47554</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21529</v>
+      </c>
+      <c r="N17" t="n">
+        <v>50.33</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260409.xlsx
+++ b/outputs/monitor_xlsx/20260409.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>95094</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>44119</v>
       </c>
       <c r="H4" t="n">
-        <v>54985</v>
+        <v>99104</v>
       </c>
       <c r="I4" t="n">
         <v>890</v>
       </c>
       <c r="J4" t="n">
-        <v>3584</v>
+        <v>4474</v>
       </c>
       <c r="K4" t="n">
         <v>15055</v>
@@ -1274,11 +1273,14 @@
         <v>10612</v>
       </c>
       <c r="M4" t="n">
-        <v>50620</v>
+        <v>61232</v>
       </c>
       <c r="N4" t="n">
         <v>-4628703</v>
       </c>
+      <c r="O4" t="n">
+        <v>4.31</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>806</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-2.89</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>1841</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-662</v>
       </c>
       <c r="H5" t="n">
-        <v>1243</v>
+        <v>581</v>
       </c>
       <c r="I5" t="n">
         <v>88</v>
       </c>
       <c r="J5" t="n">
-        <v>-296</v>
+        <v>-208</v>
       </c>
       <c r="K5" t="n">
         <v>104</v>
@@ -1329,11 +1331,14 @@
         <v>2694</v>
       </c>
       <c r="M5" t="n">
-        <v>10718</v>
+        <v>13412</v>
       </c>
       <c r="N5" t="n">
         <v>-78970</v>
       </c>
+      <c r="O5" t="n">
+        <v>-7.78</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1645</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>15129</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1053</v>
       </c>
       <c r="H6" t="n">
-        <v>5780</v>
+        <v>6834</v>
       </c>
       <c r="I6" t="n">
         <v>-98</v>
       </c>
       <c r="J6" t="n">
-        <v>532</v>
+        <v>434</v>
       </c>
       <c r="K6" t="n">
         <v>300</v>
@@ -1384,11 +1389,14 @@
         <v>4902</v>
       </c>
       <c r="M6" t="n">
-        <v>21311</v>
+        <v>26213</v>
       </c>
       <c r="N6" t="n">
         <v>-649299</v>
       </c>
+      <c r="O6" t="n">
+        <v>12.11</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="7" t="n">
         <v>1955</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0.26</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>36054</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>722</v>
       </c>
       <c r="H7" t="n">
-        <v>21070</v>
+        <v>21792</v>
       </c>
       <c r="I7" t="n">
         <v>-104</v>
       </c>
       <c r="J7" t="n">
-        <v>1313</v>
+        <v>1209</v>
       </c>
       <c r="K7" t="n">
         <v>737</v>
@@ -1439,11 +1447,14 @@
         <v>26636</v>
       </c>
       <c r="M7" t="n">
-        <v>105748</v>
+        <v>132384</v>
       </c>
       <c r="N7" t="n">
         <v>-6483090</v>
       </c>
+      <c r="O7" t="n">
+        <v>5.41</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1690</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-1.17</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>3271</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-440</v>
       </c>
       <c r="H8" t="n">
-        <v>-1923</v>
+        <v>-2363</v>
       </c>
       <c r="I8" t="n">
         <v>65</v>
       </c>
       <c r="J8" t="n">
-        <v>1091</v>
+        <v>1157</v>
       </c>
       <c r="K8" t="n">
         <v>106</v>
@@ -1494,11 +1505,14 @@
         <v>1773</v>
       </c>
       <c r="M8" t="n">
-        <v>7647</v>
+        <v>9420</v>
       </c>
       <c r="N8" t="n">
         <v>-140275</v>
       </c>
+      <c r="O8" t="n">
+        <v>7.03</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1521,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1840</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>6.67</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>6396</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>697</v>
       </c>
       <c r="H9" t="n">
-        <v>-331</v>
+        <v>366</v>
       </c>
       <c r="I9" t="n">
         <v>379</v>
       </c>
       <c r="J9" t="n">
-        <v>336</v>
+        <v>716</v>
       </c>
       <c r="K9" t="n">
         <v>196</v>
@@ -1549,11 +1563,14 @@
         <v>1825</v>
       </c>
       <c r="M9" t="n">
-        <v>8621</v>
+        <v>10446</v>
       </c>
       <c r="N9" t="n">
         <v>-106299</v>
       </c>
+      <c r="O9" t="n">
+        <v>17.07</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>3220</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>1.58</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>3254</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>95</v>
       </c>
       <c r="H10" t="n">
-        <v>699</v>
+        <v>794</v>
       </c>
       <c r="I10" t="n">
         <v>60</v>
       </c>
       <c r="J10" t="n">
-        <v>555</v>
+        <v>615</v>
       </c>
       <c r="K10" t="n">
         <v>90</v>
@@ -1604,11 +1621,14 @@
         <v>1877</v>
       </c>
       <c r="M10" t="n">
-        <v>7482</v>
+        <v>9359</v>
       </c>
       <c r="N10" t="n">
         <v>-89546</v>
       </c>
+      <c r="O10" t="n">
+        <v>15.15</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2115</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-2.31</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>2783</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-187</v>
       </c>
       <c r="H11" t="n">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="I11" t="n">
         <v>-199</v>
       </c>
       <c r="J11" t="n">
-        <v>185</v>
+        <v>-14</v>
       </c>
       <c r="K11" t="n">
         <v>81</v>
@@ -1659,11 +1679,14 @@
         <v>3887</v>
       </c>
       <c r="M11" t="n">
-        <v>15364</v>
+        <v>19251</v>
       </c>
       <c r="N11" t="n">
         <v>-19419</v>
       </c>
+      <c r="O11" t="n">
+        <v>8.59</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>7995</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2.37</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>133</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>-12</v>
       </c>
       <c r="H12" t="n">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>-248</v>
+        <v>-242</v>
       </c>
       <c r="K12" t="n">
         <v>7</v>
@@ -1714,11 +1737,14 @@
         <v>317</v>
       </c>
       <c r="M12" t="n">
-        <v>1305</v>
+        <v>1622</v>
       </c>
       <c r="N12" t="n">
         <v>-8993</v>
       </c>
+      <c r="O12" t="n">
+        <v>9.619999999999999</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>226</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="I13" t="n">
         <v>-68</v>
       </c>
       <c r="J13" t="n">
-        <v>587</v>
+        <v>519</v>
       </c>
       <c r="K13" t="n">
         <v>26</v>
@@ -1769,11 +1795,14 @@
         <v>17</v>
       </c>
       <c r="M13" t="n">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,20 +1825,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>93</v>
+        <v>116</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1821,11 +1853,14 @@
         <v>-151</v>
       </c>
       <c r="M14" t="n">
-        <v>-538</v>
+        <v>-689</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1848,20 +1883,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>-383</v>
       </c>
       <c r="H15" t="n">
-        <v>485</v>
+        <v>102</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
@@ -1873,11 +1911,14 @@
         <v>-64</v>
       </c>
       <c r="M15" t="n">
-        <v>-270</v>
+        <v>-334</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1900,26 +1941,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>-31</v>
       </c>
       <c r="H16" t="n">
-        <v>-106</v>
+        <v>-137</v>
       </c>
       <c r="I16" t="n">
         <v>53</v>
       </c>
       <c r="J16" t="n">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1928,11 +1969,14 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1950,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>576</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>6.86</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1465</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-82</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>829</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>2462</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>31</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>9842</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>47554</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-21529</v>
       </c>
-      <c r="N17" t="n">
-        <v>50.33</v>
+      <c r="O17" t="n">
+        <v>48.41</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260409.xlsx
+++ b/outputs/monitor_xlsx/20260409.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>48.41</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1575</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8422</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-728</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-5999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-178</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1010</v>
+      </c>
+      <c r="K18" t="n">
+        <v>185</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6500</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32156</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400967</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>625</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43182</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-217</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1682</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-63</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5660</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1728</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34843</v>
+      </c>
+      <c r="M19" t="n">
+        <v>170293</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393593</v>
+      </c>
+      <c r="O19" t="n">
+        <v>19.19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>669</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24577</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>4210</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7288</v>
+      </c>
+      <c r="I20" t="n">
+        <v>777</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4913</v>
+      </c>
+      <c r="K20" t="n">
+        <v>973</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8354</v>
+      </c>
+      <c r="M20" t="n">
+        <v>41960</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160909</v>
+      </c>
+      <c r="O20" t="n">
+        <v>20.52</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
